--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d7510737b73420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb2bcbc7e0b424fa8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb2bcbc7e0b424fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1fe0b18508ed42b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1fe0b18508ed42b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R611e3c13f23e490b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R611e3c13f23e490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6664662e65ff41d2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6664662e65ff41d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf2c880698a648fb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf2c880698a648fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb545e3683224012"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb545e3683224012"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3fbb71bbb8e437e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3fbb71bbb8e437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3310c4af30d4405"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3310c4af30d4405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8618fd1bd31f47cb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8618fd1bd31f47cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf399621131854842"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf399621131854842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rabc5fdc0a5a54201"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rabc5fdc0a5a54201"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R216dc5b9b2864ea6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R216dc5b9b2864ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea3189bd64db43b0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea3189bd64db43b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R635fe4d0336f4937"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ColumnWidthsAndRowHeights/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R635fe4d0336f4937"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0ad78f51942148b8"/>
   </x:sheets>
 </x:workbook>
 </file>
